--- a/artfynd/A 49611-2025 artfynd.xlsx
+++ b/artfynd/A 49611-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>7000396</v>
+        <v>7000385</v>
       </c>
       <c r="B2" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>413807.9527881331</v>
+        <v>413721</v>
       </c>
       <c r="R2" t="n">
-        <v>6966557.85966726</v>
+        <v>6966650</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2013-07-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2013-09-03</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-08-23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>7000397</v>
+        <v>7000395</v>
       </c>
       <c r="B3" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -831,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>413821.3122013522</v>
+        <v>413789</v>
       </c>
       <c r="R3" t="n">
-        <v>6966543.3296522</v>
+        <v>6966542</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -864,19 +844,9 @@
           <t>2013-07-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2013-09-04</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-09-02</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,15 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>7000395</v>
+        <v>7000396</v>
       </c>
       <c r="B4" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -947,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>413789.2117676652</v>
+        <v>413808</v>
       </c>
       <c r="R4" t="n">
-        <v>6966541.885886763</v>
+        <v>6966558</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -980,19 +945,9 @@
           <t>2013-07-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2013-09-02</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-09-03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,15 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120096943</v>
+        <v>7000397</v>
       </c>
       <c r="B5" t="n">
-        <v>92048</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1039,37 +989,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2079</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Långtjärnberget, Hjd</t>
+          <t>Björnhåberget, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>413950</v>
+        <v>413821</v>
       </c>
       <c r="R5" t="n">
-        <v>6966665</v>
+        <v>6966543</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1093,22 +1043,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>12:35</t>
+          <t>2013-07-01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>12:35</t>
+          <t>2013-09-04</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,65 +1063,64 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Hugo Ström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Hugo Ström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120096936</v>
+        <v>7000406</v>
       </c>
       <c r="B6" t="n">
-        <v>96891</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221941</v>
+        <v>1962</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Långtjärnberget, Hjd</t>
+          <t>Björnhåberget, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>413957</v>
+        <v>414049</v>
       </c>
       <c r="R6" t="n">
-        <v>6966625</v>
+        <v>6966529</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1205,22 +1144,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>12:37</t>
+          <t>2013-07-01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>12:37</t>
+          <t>2013-09-12</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,15 +1164,982 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
+          <t>Hugo Ström</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Hugo Ström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>120096941</v>
+      </c>
+      <c r="B7" t="n">
+        <v>91962</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>2079</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Nordtagging</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Odonticium romellii</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>413934</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6966582</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
           <t>Johan Råghall</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
+      <c r="AX7" t="inlineStr">
         <is>
           <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr"/>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>120096943</v>
+      </c>
+      <c r="B8" t="n">
+        <v>91962</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>2079</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Nordtagging</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Odonticium romellii</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>413950</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6966665</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>120096944</v>
+      </c>
+      <c r="B9" t="n">
+        <v>91962</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>2079</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Nordtagging</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Odonticium romellii</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>413968</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6966758</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>120096988</v>
+      </c>
+      <c r="B10" t="n">
+        <v>78730</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>413934</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6966582</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>120096989</v>
+      </c>
+      <c r="B11" t="n">
+        <v>78730</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>413968</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6966758</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>120096990</v>
+      </c>
+      <c r="B12" t="n">
+        <v>78730</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>413973</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6966788</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>120096980</v>
+      </c>
+      <c r="B13" t="n">
+        <v>78334</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>413968</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6966758</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>120096936</v>
+      </c>
+      <c r="B14" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>413957</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6966625</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>120096926</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>413968</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6966758</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 49611-2025 artfynd.xlsx
+++ b/artfynd/A 49611-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7000385</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7000395</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7000396</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7000397</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7000406</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1284,6 +1314,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096941</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1391,6 +1426,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096943</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1498,6 +1538,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096944</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1605,6 +1650,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096988</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1712,6 +1762,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096989</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1819,6 +1874,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096990</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1926,6 +1986,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096980</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2033,6 +2098,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096936</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2140,8 +2210,29 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096926</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 49611-2025 artfynd.xlsx
+++ b/artfynd/A 49611-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ15"/>
+  <dimension ref="A1:AZ28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,48 +680,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>7000385</v>
+        <v>135784648</v>
       </c>
       <c r="B2" t="n">
-        <v>78993</v>
+        <v>92294</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>353</v>
+        <v>65</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Björnhåberget, Hjd</t>
+          <t>Putten, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>413721</v>
+        <v>413927</v>
       </c>
       <c r="R2" t="n">
-        <v>6966650</v>
+        <v>6966727</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2013-07-01</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2013-08-23</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,69 +765,65 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/7000385</t>
+          <t>https://artportalen.se/Sighting/135784648</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>7000395</v>
+        <v>135784644</v>
       </c>
       <c r="B3" t="n">
-        <v>78993</v>
+        <v>92443</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>298</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Laxgröppa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Meruliopsis rubicunda</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Litsch.) Spirin &amp; K.H.Larss.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Björnhåberget, Hjd</t>
+          <t>Putten, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>413789</v>
+        <v>413901</v>
       </c>
       <c r="R3" t="n">
-        <v>6966542</v>
+        <v>6966647</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -851,12 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2013-07-01</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2013-09-02</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -871,28 +867,24 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/7000395</t>
+          <t>https://artportalen.se/Sighting/135784644</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>7000396</v>
+        <v>7000385</v>
       </c>
       <c r="B4" t="n">
         <v>78993</v>
@@ -927,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>413808</v>
+        <v>413721</v>
       </c>
       <c r="R4" t="n">
-        <v>6966558</v>
+        <v>6966650</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -962,7 +954,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2013-09-03</t>
+          <t>2013-08-23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -992,13 +984,13 @@
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/7000396</t>
+          <t>https://artportalen.se/Sighting/7000385</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>7000397</v>
+        <v>7000395</v>
       </c>
       <c r="B5" t="n">
         <v>78993</v>
@@ -1033,10 +1025,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>413821</v>
+        <v>413789</v>
       </c>
       <c r="R5" t="n">
-        <v>6966543</v>
+        <v>6966542</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1068,7 +1060,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2013-09-04</t>
+          <t>2013-09-02</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,16 +1090,16 @@
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/7000397</t>
+          <t>https://artportalen.se/Sighting/7000395</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>7000406</v>
+        <v>7000396</v>
       </c>
       <c r="B6" t="n">
-        <v>90932</v>
+        <v>78993</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1115,21 +1107,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1962</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1131,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>414049</v>
+        <v>413808</v>
       </c>
       <c r="R6" t="n">
-        <v>6966529</v>
+        <v>6966558</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1174,7 +1166,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2013-09-12</t>
+          <t>2013-09-03</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1204,16 +1196,16 @@
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/7000406</t>
+          <t>https://artportalen.se/Sighting/7000396</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120096941</v>
+        <v>7000397</v>
       </c>
       <c r="B7" t="n">
-        <v>91962</v>
+        <v>78993</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,37 +1213,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2079</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Långtjärnberget, Hjd</t>
+          <t>Björnhåberget, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>413934</v>
+        <v>413821</v>
       </c>
       <c r="R7" t="n">
-        <v>6966582</v>
+        <v>6966543</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1275,22 +1267,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>12:42</t>
+          <t>2013-07-01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>12:42</t>
+          <t>2013-09-04</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1305,62 +1287,66 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Hugo Ström</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Hugo Ström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120096941</t>
+          <t>https://artportalen.se/Sighting/7000397</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120096943</v>
+        <v>135784642</v>
       </c>
       <c r="B8" t="n">
-        <v>91962</v>
+        <v>92227</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2079</v>
+        <v>1503</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Långtjärnberget, Hjd</t>
+          <t>Putten, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>413950</v>
+        <v>413742</v>
       </c>
       <c r="R8" t="n">
-        <v>6966665</v>
+        <v>6966614</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,22 +1373,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>12:35</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>12:35</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1417,27 +1393,27 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120096943</t>
+          <t>https://artportalen.se/Sighting/135784642</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120096944</v>
+        <v>135784639</v>
       </c>
       <c r="B9" t="n">
-        <v>91962</v>
+        <v>92241</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1445,34 +1421,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2079</v>
+        <v>1588</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Långtjärnberget, Hjd</t>
+          <t>Putten, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>413968</v>
+        <v>413741</v>
       </c>
       <c r="R9" t="n">
-        <v>6966758</v>
+        <v>6966620</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1499,22 +1475,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>12:25</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>12:25</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1529,27 +1495,27 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120096944</t>
+          <t>https://artportalen.se/Sighting/135784639</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120096988</v>
+        <v>7000406</v>
       </c>
       <c r="B10" t="n">
-        <v>78730</v>
+        <v>90932</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1557,37 +1523,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6437</v>
+        <v>1962</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Långtjärnberget, Hjd</t>
+          <t>Björnhåberget, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>413934</v>
+        <v>414049</v>
       </c>
       <c r="R10" t="n">
-        <v>6966582</v>
+        <v>6966529</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1611,22 +1577,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>12:43</t>
+          <t>2013-07-01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>12:43</t>
+          <t>2013-09-12</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1641,27 +1597,31 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Hugo Ström</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
+          <t>Hugo Ström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120096988</t>
+          <t>https://artportalen.se/Sighting/7000406</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120096989</v>
+        <v>135784649</v>
       </c>
       <c r="B11" t="n">
-        <v>78730</v>
+        <v>91069</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1669,34 +1629,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6437</v>
+        <v>1962</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Långtjärnberget, Hjd</t>
+          <t>Putten, Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>413968</v>
+        <v>413926</v>
       </c>
       <c r="R11" t="n">
-        <v>6966758</v>
+        <v>6966725</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1723,22 +1683,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>12:25</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>12:25</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1753,27 +1703,27 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120096989</t>
+          <t>https://artportalen.se/Sighting/135784649</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120096990</v>
+        <v>120096941</v>
       </c>
       <c r="B12" t="n">
-        <v>78730</v>
+        <v>91962</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1781,21 +1731,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6437</v>
+        <v>2079</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1805,10 +1755,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>413973</v>
+        <v>413934</v>
       </c>
       <c r="R12" t="n">
-        <v>6966788</v>
+        <v>6966582</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1840,7 +1790,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1850,7 +1800,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1876,16 +1826,16 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120096990</t>
+          <t>https://artportalen.se/Sighting/120096941</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120096980</v>
+        <v>120096943</v>
       </c>
       <c r="B13" t="n">
-        <v>78334</v>
+        <v>91962</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1893,21 +1843,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6487</v>
+        <v>2079</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1917,10 +1867,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>413968</v>
+        <v>413950</v>
       </c>
       <c r="R13" t="n">
-        <v>6966758</v>
+        <v>6966665</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1952,7 +1902,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1962,7 +1912,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1988,38 +1938,38 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120096980</t>
+          <t>https://artportalen.se/Sighting/120096943</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120096936</v>
+        <v>120096944</v>
       </c>
       <c r="B14" t="n">
-        <v>97989</v>
+        <v>91962</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221941</v>
+        <v>2079</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2029,10 +1979,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>413957</v>
+        <v>413968</v>
       </c>
       <c r="R14" t="n">
-        <v>6966625</v>
+        <v>6966758</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2064,7 +2014,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2074,7 +2024,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2100,16 +2050,16 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120096936</t>
+          <t>https://artportalen.se/Sighting/120096944</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120096926</v>
+        <v>135784638</v>
       </c>
       <c r="B15" t="n">
-        <v>79917</v>
+        <v>91970</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2117,34 +2067,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>229821</v>
+        <v>3242</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Långtjärnberget, Hjd</t>
+          <t>Putten, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>413968</v>
+        <v>413740</v>
       </c>
       <c r="R15" t="n">
-        <v>6966758</v>
+        <v>6966625</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2171,22 +2121,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>12:25</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>12:25</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2201,16 +2141,1402 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784638</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135784640</v>
+      </c>
+      <c r="B16" t="n">
+        <v>92011</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Putten, Hjd</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>413742</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6966614</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784640</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>120096988</v>
+      </c>
+      <c r="B17" t="n">
+        <v>78730</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>413934</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6966582</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096988</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>120096989</v>
+      </c>
+      <c r="B18" t="n">
+        <v>78730</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>413968</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6966758</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096989</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>120096990</v>
+      </c>
+      <c r="B19" t="n">
+        <v>78730</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>413973</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6966788</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096990</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135784646</v>
+      </c>
+      <c r="B20" t="n">
+        <v>78844</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Putten, Hjd</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>413899</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6966659</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784646</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135784635</v>
+      </c>
+      <c r="B21" t="n">
+        <v>80060</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Putten, Hjd</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>413755</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6966653</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784635</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>135784637</v>
+      </c>
+      <c r="B22" t="n">
+        <v>80060</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Putten, Hjd</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>413752</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6966651</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784637</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>120096980</v>
+      </c>
+      <c r="B23" t="n">
+        <v>78334</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>413968</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6966758</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096980</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>135784647</v>
+      </c>
+      <c r="B24" t="n">
+        <v>78445</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Putten, Hjd</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>413899</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6966658</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784647</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>120096936</v>
+      </c>
+      <c r="B25" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>413957</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6966625</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120096936</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>135784636</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79199</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Putten, Hjd</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>413755</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6966653</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784636</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>135784645</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79199</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Putten, Hjd</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>413897</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6966658</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784645</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>120096926</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Långtjärnberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>413968</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6966758</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Johan Råghall, Bjarne Tutturen, Henrik Ekvall</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/120096926</t>
         </is>
@@ -2232,6 +3558,19 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 49611-2025 artfynd.xlsx
+++ b/artfynd/A 49611-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135784648</v>
       </c>
       <c r="B2" t="n">
-        <v>92294</v>
+        <v>92296</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135784644</v>
       </c>
       <c r="B3" t="n">
-        <v>92443</v>
+        <v>92445</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1311,7 +1311,7 @@
         <v>135784642</v>
       </c>
       <c r="B8" t="n">
-        <v>92227</v>
+        <v>92229</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>135784639</v>
       </c>
       <c r="B9" t="n">
-        <v>92241</v>
+        <v>92243</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>135784649</v>
       </c>
       <c r="B11" t="n">
-        <v>91069</v>
+        <v>91071</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2059,7 +2059,7 @@
         <v>135784638</v>
       </c>
       <c r="B15" t="n">
-        <v>91970</v>
+        <v>91972</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
         <v>135784640</v>
       </c>
       <c r="B16" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 49611-2025 artfynd.xlsx
+++ b/artfynd/A 49611-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135784648</v>
       </c>
       <c r="B2" t="n">
-        <v>92296</v>
+        <v>92310</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135784644</v>
       </c>
       <c r="B3" t="n">
-        <v>92445</v>
+        <v>92459</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1311,7 +1311,7 @@
         <v>135784642</v>
       </c>
       <c r="B8" t="n">
-        <v>92229</v>
+        <v>92243</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>135784639</v>
       </c>
       <c r="B9" t="n">
-        <v>92243</v>
+        <v>92257</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>135784649</v>
       </c>
       <c r="B11" t="n">
-        <v>91071</v>
+        <v>91073</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2059,7 +2059,7 @@
         <v>135784638</v>
       </c>
       <c r="B15" t="n">
-        <v>91972</v>
+        <v>91986</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
         <v>135784640</v>
       </c>
       <c r="B16" t="n">
-        <v>92013</v>
+        <v>92027</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>135784646</v>
       </c>
       <c r="B20" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2701,7 +2701,7 @@
         <v>135784635</v>
       </c>
       <c r="B21" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         <v>135784637</v>
       </c>
       <c r="B22" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
         <v>135784647</v>
       </c>
       <c r="B24" t="n">
-        <v>78445</v>
+        <v>78447</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3231,7 +3231,7 @@
         <v>135784636</v>
       </c>
       <c r="B26" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3333,7 +3333,7 @@
         <v>135784645</v>
       </c>
       <c r="B27" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 49611-2025 artfynd.xlsx
+++ b/artfynd/A 49611-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135784648</v>
       </c>
       <c r="B2" t="n">
-        <v>92310</v>
+        <v>92311</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135784644</v>
       </c>
       <c r="B3" t="n">
-        <v>92459</v>
+        <v>92460</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1311,7 +1311,7 @@
         <v>135784642</v>
       </c>
       <c r="B8" t="n">
-        <v>92243</v>
+        <v>92244</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>135784639</v>
       </c>
       <c r="B9" t="n">
-        <v>92257</v>
+        <v>92258</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>135784649</v>
       </c>
       <c r="B11" t="n">
-        <v>91073</v>
+        <v>91074</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2059,7 +2059,7 @@
         <v>135784638</v>
       </c>
       <c r="B15" t="n">
-        <v>91986</v>
+        <v>91987</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
         <v>135784640</v>
       </c>
       <c r="B16" t="n">
-        <v>92027</v>
+        <v>92028</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>135784646</v>
       </c>
       <c r="B20" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2701,7 +2701,7 @@
         <v>135784635</v>
       </c>
       <c r="B21" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         <v>135784637</v>
       </c>
       <c r="B22" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
         <v>135784647</v>
       </c>
       <c r="B24" t="n">
-        <v>78447</v>
+        <v>78448</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3231,7 +3231,7 @@
         <v>135784636</v>
       </c>
       <c r="B26" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3333,7 +3333,7 @@
         <v>135784645</v>
       </c>
       <c r="B27" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 49611-2025 artfynd.xlsx
+++ b/artfynd/A 49611-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135784648</v>
       </c>
       <c r="B2" t="n">
-        <v>92311</v>
+        <v>92312</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135784644</v>
       </c>
       <c r="B3" t="n">
-        <v>92460</v>
+        <v>92461</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1311,7 +1311,7 @@
         <v>135784642</v>
       </c>
       <c r="B8" t="n">
-        <v>92244</v>
+        <v>92245</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>135784639</v>
       </c>
       <c r="B9" t="n">
-        <v>92258</v>
+        <v>92259</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>135784649</v>
       </c>
       <c r="B11" t="n">
-        <v>91074</v>
+        <v>91075</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2059,7 +2059,7 @@
         <v>135784638</v>
       </c>
       <c r="B15" t="n">
-        <v>91987</v>
+        <v>91988</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
         <v>135784640</v>
       </c>
       <c r="B16" t="n">
-        <v>92028</v>
+        <v>92029</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 49611-2025 artfynd.xlsx
+++ b/artfynd/A 49611-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135784648</v>
       </c>
       <c r="B2" t="n">
-        <v>92312</v>
+        <v>92313</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135784644</v>
       </c>
       <c r="B3" t="n">
-        <v>92461</v>
+        <v>92462</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1311,7 +1311,7 @@
         <v>135784642</v>
       </c>
       <c r="B8" t="n">
-        <v>92245</v>
+        <v>92246</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>135784639</v>
       </c>
       <c r="B9" t="n">
-        <v>92259</v>
+        <v>92260</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>135784649</v>
       </c>
       <c r="B11" t="n">
-        <v>91075</v>
+        <v>91076</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2059,7 +2059,7 @@
         <v>135784638</v>
       </c>
       <c r="B15" t="n">
-        <v>91988</v>
+        <v>91989</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
         <v>135784640</v>
       </c>
       <c r="B16" t="n">
-        <v>92029</v>
+        <v>92030</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>135784646</v>
       </c>
       <c r="B20" t="n">
-        <v>78847</v>
+        <v>78848</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2701,7 +2701,7 @@
         <v>135784635</v>
       </c>
       <c r="B21" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         <v>135784637</v>
       </c>
       <c r="B22" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
         <v>135784647</v>
       </c>
       <c r="B24" t="n">
-        <v>78448</v>
+        <v>78449</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3231,7 +3231,7 @@
         <v>135784636</v>
       </c>
       <c r="B26" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3333,7 +3333,7 @@
         <v>135784645</v>
       </c>
       <c r="B27" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 49611-2025 artfynd.xlsx
+++ b/artfynd/A 49611-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135784648</v>
       </c>
       <c r="B2" t="n">
-        <v>92313</v>
+        <v>92319</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135784644</v>
       </c>
       <c r="B3" t="n">
-        <v>92462</v>
+        <v>92468</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1311,7 +1311,7 @@
         <v>135784642</v>
       </c>
       <c r="B8" t="n">
-        <v>92246</v>
+        <v>92252</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>135784639</v>
       </c>
       <c r="B9" t="n">
-        <v>92260</v>
+        <v>92266</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>135784649</v>
       </c>
       <c r="B11" t="n">
-        <v>91076</v>
+        <v>91082</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2059,7 +2059,7 @@
         <v>135784638</v>
       </c>
       <c r="B15" t="n">
-        <v>91989</v>
+        <v>91995</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
         <v>135784640</v>
       </c>
       <c r="B16" t="n">
-        <v>92030</v>
+        <v>92036</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>135784646</v>
       </c>
       <c r="B20" t="n">
-        <v>78848</v>
+        <v>78852</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2701,7 +2701,7 @@
         <v>135784635</v>
       </c>
       <c r="B21" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         <v>135784637</v>
       </c>
       <c r="B22" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
         <v>135784647</v>
       </c>
       <c r="B24" t="n">
-        <v>78449</v>
+        <v>78453</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3231,7 +3231,7 @@
         <v>135784636</v>
       </c>
       <c r="B26" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3333,7 +3333,7 @@
         <v>135784645</v>
       </c>
       <c r="B27" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 49611-2025 artfynd.xlsx
+++ b/artfynd/A 49611-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135784648</v>
       </c>
       <c r="B2" t="n">
-        <v>92319</v>
+        <v>92320</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135784644</v>
       </c>
       <c r="B3" t="n">
-        <v>92468</v>
+        <v>92469</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1311,7 +1311,7 @@
         <v>135784642</v>
       </c>
       <c r="B8" t="n">
-        <v>92252</v>
+        <v>92253</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>135784639</v>
       </c>
       <c r="B9" t="n">
-        <v>92266</v>
+        <v>92267</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>135784649</v>
       </c>
       <c r="B11" t="n">
-        <v>91082</v>
+        <v>91083</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2059,7 +2059,7 @@
         <v>135784638</v>
       </c>
       <c r="B15" t="n">
-        <v>91995</v>
+        <v>91996</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
         <v>135784640</v>
       </c>
       <c r="B16" t="n">
-        <v>92036</v>
+        <v>92037</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>135784646</v>
       </c>
       <c r="B20" t="n">
-        <v>78852</v>
+        <v>78853</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2701,7 +2701,7 @@
         <v>135784635</v>
       </c>
       <c r="B21" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         <v>135784637</v>
       </c>
       <c r="B22" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
         <v>135784647</v>
       </c>
       <c r="B24" t="n">
-        <v>78453</v>
+        <v>78454</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3231,7 +3231,7 @@
         <v>135784636</v>
       </c>
       <c r="B26" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3333,7 +3333,7 @@
         <v>135784645</v>
       </c>
       <c r="B27" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 49611-2025 artfynd.xlsx
+++ b/artfynd/A 49611-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135784648</v>
       </c>
       <c r="B2" t="n">
-        <v>92320</v>
+        <v>92326</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135784644</v>
       </c>
       <c r="B3" t="n">
-        <v>92469</v>
+        <v>92475</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1311,7 +1311,7 @@
         <v>135784642</v>
       </c>
       <c r="B8" t="n">
-        <v>92253</v>
+        <v>92259</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>135784639</v>
       </c>
       <c r="B9" t="n">
-        <v>92267</v>
+        <v>92273</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>135784649</v>
       </c>
       <c r="B11" t="n">
-        <v>91083</v>
+        <v>91089</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2059,7 +2059,7 @@
         <v>135784638</v>
       </c>
       <c r="B15" t="n">
-        <v>91996</v>
+        <v>92002</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
         <v>135784640</v>
       </c>
       <c r="B16" t="n">
-        <v>92037</v>
+        <v>92043</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>135784646</v>
       </c>
       <c r="B20" t="n">
-        <v>78853</v>
+        <v>78857</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2701,7 +2701,7 @@
         <v>135784635</v>
       </c>
       <c r="B21" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         <v>135784637</v>
       </c>
       <c r="B22" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
         <v>135784647</v>
       </c>
       <c r="B24" t="n">
-        <v>78454</v>
+        <v>78458</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3231,7 +3231,7 @@
         <v>135784636</v>
       </c>
       <c r="B26" t="n">
-        <v>79208</v>
+        <v>79212</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3333,7 +3333,7 @@
         <v>135784645</v>
       </c>
       <c r="B27" t="n">
-        <v>79208</v>
+        <v>79212</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 49611-2025 artfynd.xlsx
+++ b/artfynd/A 49611-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135784648</v>
       </c>
       <c r="B2" t="n">
-        <v>92326</v>
+        <v>92333</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135784644</v>
       </c>
       <c r="B3" t="n">
-        <v>92475</v>
+        <v>92482</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1311,7 +1311,7 @@
         <v>135784642</v>
       </c>
       <c r="B8" t="n">
-        <v>92259</v>
+        <v>92266</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>135784639</v>
       </c>
       <c r="B9" t="n">
-        <v>92273</v>
+        <v>92280</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>135784649</v>
       </c>
       <c r="B11" t="n">
-        <v>91089</v>
+        <v>91096</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2059,7 +2059,7 @@
         <v>135784638</v>
       </c>
       <c r="B15" t="n">
-        <v>92002</v>
+        <v>92009</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
         <v>135784640</v>
       </c>
       <c r="B16" t="n">
-        <v>92043</v>
+        <v>92050</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>135784646</v>
       </c>
       <c r="B20" t="n">
-        <v>78857</v>
+        <v>78863</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2701,7 +2701,7 @@
         <v>135784635</v>
       </c>
       <c r="B21" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         <v>135784637</v>
       </c>
       <c r="B22" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
         <v>135784647</v>
       </c>
       <c r="B24" t="n">
-        <v>78458</v>
+        <v>78464</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3231,7 +3231,7 @@
         <v>135784636</v>
       </c>
       <c r="B26" t="n">
-        <v>79212</v>
+        <v>79218</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3333,7 +3333,7 @@
         <v>135784645</v>
       </c>
       <c r="B27" t="n">
-        <v>79212</v>
+        <v>79218</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 49611-2025 artfynd.xlsx
+++ b/artfynd/A 49611-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135784648</v>
       </c>
       <c r="B2" t="n">
-        <v>92333</v>
+        <v>92334</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135784644</v>
       </c>
       <c r="B3" t="n">
-        <v>92482</v>
+        <v>92483</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1311,7 +1311,7 @@
         <v>135784642</v>
       </c>
       <c r="B8" t="n">
-        <v>92266</v>
+        <v>92267</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>135784639</v>
       </c>
       <c r="B9" t="n">
-        <v>92280</v>
+        <v>92281</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>135784649</v>
       </c>
       <c r="B11" t="n">
-        <v>91096</v>
+        <v>91097</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2059,7 +2059,7 @@
         <v>135784638</v>
       </c>
       <c r="B15" t="n">
-        <v>92009</v>
+        <v>92010</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
         <v>135784640</v>
       </c>
       <c r="B16" t="n">
-        <v>92050</v>
+        <v>92051</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
